--- a/.agent/fixtures/documents/vajra_payment_ledger.xlsx
+++ b/.agent/fixtures/documents/vajra_payment_ledger.xlsx
@@ -469,8 +469,10 @@
           <t>SO/2026/009</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>240000</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2,40,000</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -499,8 +501,10 @@
           <t>Invoice TOI/2026/088</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>420000000</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4,20,00,000</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
